--- a/ig/mc-add-link-doc/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1688,7 +1688,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Synonyme MOS : typeBAL 
+    <t>Synonyme : typeBAL 
 Valeurs possibles :
 ORG pour une BAL organisationnelle;
 APP pour une BAL applicative;
@@ -1740,7 +1740,7 @@
     <t>Description fonctionnelle de la boîte aux lettres.</t>
   </si>
   <si>
-    <t>Synonyme MOS : description</t>
+    <t>Synonyme : description</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
@@ -1788,7 +1788,7 @@
     <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
   </si>
   <si>
-    <t>Synonyme MOS : serviceRattachement</t>
+    <t>Synonyme : serviceRattachement</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
@@ -1837,7 +1837,7 @@
 - N : Dématérialisation refusée.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dematerialisation</t>
+    <t>Synonyme : dematerialisation</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
@@ -1862,7 +1862,7 @@
 N: La boîte aux lettres peut être publiée</t>
   </si>
   <si>
-    <t>Synonyme MOS : listeRouge</t>
+    <t>Synonyme : listeRouge</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.id</t>
